--- a/config/auto_configs/2019_Hyundai_Genesis_G70(IK)_G 2.0 T-GDI.xlsx
+++ b/config/auto_configs/2019_Hyundai_Genesis_G70(IK)_G 2.0 T-GDI.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="VIN_YMME" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="NWS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VIN_YMME" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NWS" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -492,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -745,7 +745,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>HMA_0045C</t>
+          <t>HMA_0045B</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>HMA_0045C</t>
+          <t>HMA_0045B</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>HMA_0045C</t>
+          <t>HMA_0045B</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>HMA_0045C</t>
+          <t>HMA_0045B</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -833,7 +833,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HMA_0045B</t>
+          <t>HMA_0045C</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>HMA_0045B</t>
+          <t>HMA_0045C</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>HMA_0045B</t>
+          <t>HMA_0045C</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>HMA_0045B</t>
+          <t>HMA_0045C</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -908,6 +908,556 @@
         </is>
       </c>
       <c r="D19" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>HMA_0027E</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>P040100</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>HMA_0027E</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>P042B00</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>HMA_0027E</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>P043E00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>HMA_0027E</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>P043F00</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>HMA_0027E</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>P242B00</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>HMA_0027E</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>P242E00</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>HMA_0027E</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>P247800</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>HMA_0027E</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>P247900</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>HMA_0027E</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>P247A00</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>HMA_0027E</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>U012A00</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>HMA_0027E</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>U042B00</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>HMA_00346</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>P075A00</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>HMA_00346</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>P076A00</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>HMA_00346</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>P076D00</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>HMA_00346</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>P078500</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>HMA_00346</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>P078A00</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>HMA_00346</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>P160200</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>HMA_00346</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>U000100</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>HMA_00346</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>U010000</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>IBU-TPMS</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>HMA_00464</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>4WD</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>HMA_003F5</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>A/C</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>HMA_0032A</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>AAF</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>HMA_00356</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>AFLS</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>HMA_00462</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>AHS</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>HMA_003C1</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
         <is>
           <t>00</t>
         </is>
